--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_projets.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_projets.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Projet" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="57">
   <si>
     <t xml:space="preserve">id_projet  (si utilisé ailleurs)</t>
   </si>
@@ -181,6 +181,12 @@
   </si>
   <si>
     <t xml:space="preserve">HOBO_n°38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMS4_n°0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dendro_n°0</t>
   </si>
   <si>
     <t xml:space="preserve">id_groupe_recolte</t>
@@ -489,11 +495,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.12"/>
@@ -567,11 +572,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.83"/>
@@ -1025,6 +1029,28 @@
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1045,11 +1071,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.21"/>
@@ -1057,10 +1082,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="2"/>
     </row>

--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_projets.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_projets.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Projet" sheetId="1" state="visible" r:id="rId3"/>
@@ -183,10 +183,10 @@
     <t xml:space="preserve">HOBO_n°38</t>
   </si>
   <si>
-    <t xml:space="preserve">TMS4_n°0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dendro_n°0</t>
+    <t xml:space="preserve">TMS4_95224601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dendro_92261195</t>
   </si>
   <si>
     <t xml:space="preserve">id_groupe_recolte</t>
@@ -203,7 +203,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -239,6 +239,12 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -283,7 +289,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -305,6 +311,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1033,7 +1043,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B42" s="1" t="n">
@@ -1044,10 +1054,10 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
